--- a/segmentation/segmentation_results.xlsx
+++ b/segmentation/segmentation_results.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="105">
   <si>
     <t>n</t>
   </si>
@@ -252,21 +252,18 @@
     <t>検定対象n</t>
   </si>
   <si>
-    <t>χ²</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>漸近p</t>
-  </si>
-  <si>
-    <t>並べ替え検定p</t>
+    <t>フィッシャーの正確確率検定 p</t>
   </si>
   <si>
     <t>Cramér's V</t>
   </si>
   <si>
+    <t>（参考）χ²</t>
+  </si>
+  <si>
+    <t>（参考）df</t>
+  </si>
+  <si>
     <t>期待度数&lt;5のセル割合</t>
   </si>
   <si>
@@ -294,7 +291,10 @@
     <t>行%（セグメント内の構成比）</t>
   </si>
   <si>
-    <t>調整済み残差（|z|&gt;1.96で有意）</t>
+    <t>調整済み残差（記述用）</t>
+  </si>
+  <si>
+    <t>下位検定: セルごとの2×2フィッシャー検定 p（Holm補正）</t>
   </si>
   <si>
     <t>その他</t>
@@ -1014,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1035,7 +1035,7 @@
         <v>74</v>
       </c>
       <c r="B3">
-        <v>18.0282</v>
+        <v>0.5064</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1043,7 +1043,7 @@
         <v>75</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>0.2359</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1051,7 +1051,7 @@
         <v>76</v>
       </c>
       <c r="B5">
-        <v>0.2612</v>
+        <v>18.0282</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1059,7 +1059,7 @@
         <v>77</v>
       </c>
       <c r="B6">
-        <v>0.2695</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1067,20 +1067,12 @@
         <v>78</v>
       </c>
       <c r="B7">
-        <v>0.2359</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8">
         <v>0.5833</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1088,22 +1080,22 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
         <v>80</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>82</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>83</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>84</v>
-      </c>
-      <c r="G11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1246,7 +1238,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1254,19 +1246,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
         <v>80</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>81</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>83</v>
-      </c>
-      <c r="F21" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1391,7 +1383,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1399,16 +1391,16 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
         <v>80</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>81</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>82</v>
-      </c>
-      <c r="E31" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1511,6 +1503,130 @@
       </c>
       <c r="E37">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>0.2898</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1520,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1541,7 +1657,7 @@
         <v>74</v>
       </c>
       <c r="B3">
-        <v>4.802</v>
+        <v>0.4556</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1549,7 +1665,7 @@
         <v>75</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0.2043</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1557,7 +1673,7 @@
         <v>76</v>
       </c>
       <c r="B5">
-        <v>0.4405</v>
+        <v>4.802</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1565,7 +1681,7 @@
         <v>77</v>
       </c>
       <c r="B6">
-        <v>0.4642</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1573,20 +1689,12 @@
         <v>78</v>
       </c>
       <c r="B7">
-        <v>0.2043</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8">
         <v>0.3333</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1603,7 +1711,7 @@
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1710,7 +1818,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1813,7 +1921,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1891,6 +1999,88 @@
       </c>
       <c r="C37">
         <v>-1.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1921,7 +2111,7 @@
         <v>74</v>
       </c>
       <c r="B3">
-        <v>10.351</v>
+        <v>0.1228</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1929,7 +2119,7 @@
         <v>75</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0.2987</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1937,7 +2127,7 @@
         <v>76</v>
       </c>
       <c r="B5">
-        <v>0.0659</v>
+        <v>10.351</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1945,7 +2135,7 @@
         <v>77</v>
       </c>
       <c r="B6">
-        <v>0.0721</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1953,20 +2143,12 @@
         <v>78</v>
       </c>
       <c r="B7">
-        <v>0.2987</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8">
         <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1980,7 +2162,7 @@
         <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2069,7 +2251,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2151,7 +2333,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2229,6 +2411,88 @@
       </c>
       <c r="C37">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45">
+        <v>0.0562</v>
+      </c>
+      <c r="C45">
+        <v>0.0562</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2238,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2259,7 +2523,7 @@
         <v>74</v>
       </c>
       <c r="B3">
-        <v>23.246</v>
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2267,7 +2531,7 @@
         <v>75</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2275,7 +2539,7 @@
         <v>76</v>
       </c>
       <c r="B5">
-        <v>0.0791</v>
+        <v>23.246</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2283,7 +2547,7 @@
         <v>77</v>
       </c>
       <c r="B6">
-        <v>0.07199999999999999</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2291,20 +2555,12 @@
         <v>78</v>
       </c>
       <c r="B7">
-        <v>0.2585</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8">
         <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2324,7 +2580,7 @@
         <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2449,7 +2705,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2573,7 +2829,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2693,6 +2949,130 @@
       </c>
       <c r="E37">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>0.0057</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>0.8912</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0.7562</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2739,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2750,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3">
         <v>-0.5574747128376729</v>
@@ -2776,7 +3156,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4">
         <v>-0.1299976216298829</v>
@@ -2802,7 +3182,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5">
         <v>-0.1746485687842852</v>
@@ -2828,7 +3208,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6">
         <v>-0.5447978709999376</v>
@@ -2854,7 +3234,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2865,7 +3245,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>-1.023645559773101</v>
@@ -2891,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <v>-0.1838781302108423</v>
@@ -2917,7 +3297,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10">
         <v>0.3612939728313038</v>
@@ -2943,7 +3323,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11">
         <v>-0.3220542533230158</v>
@@ -2969,7 +3349,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>0.3439782907502662</v>
@@ -2995,7 +3375,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>0.3900039728561599</v>
@@ -3021,7 +3401,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14">
         <v>0.09231223844119693</v>
@@ -3047,7 +3427,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15">
         <v>1.430304746738134</v>
@@ -3073,7 +3453,7 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>1.01136348502193</v>
@@ -3099,7 +3479,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D17">
         <v>-0.4998374252596787</v>
@@ -3125,7 +3505,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18">
         <v>0.2607913482830148</v>
@@ -3151,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D19">
         <v>1.350831670822532</v>
@@ -3177,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20">
         <v>1.462652674166755</v>
@@ -3203,7 +3583,7 @@
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21">
         <v>-0.3498664855860121</v>
@@ -3229,7 +3609,7 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22">
         <v>-1.223955685244825</v>
@@ -3255,7 +3635,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D23">
         <v>0.5179070850451212</v>
@@ -3281,7 +3661,7 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24">
         <v>-0.05756116889432042</v>
@@ -3307,7 +3687,7 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D25">
         <v>-0.7554598042702086</v>
@@ -3333,7 +3713,7 @@
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3344,7 +3724,7 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27">
         <v>1.171836154418401</v>
@@ -3370,7 +3750,7 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D28">
         <v>0.2448824796140681</v>
@@ -3396,7 +3776,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29">
         <v>1.120174839935586</v>
@@ -3422,7 +3802,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D30">
         <v>-0.2195817119969808</v>
@@ -3448,7 +3828,7 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D31">
         <v>-0.004578590777285951</v>
@@ -3474,7 +3854,7 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32">
         <v>-1.569471018290258</v>
@@ -3500,7 +3880,7 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D33">
         <v>-1.205124956539953</v>
@@ -3526,7 +3906,7 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D34">
         <v>-0.4511592700069666</v>
@@ -3552,7 +3932,7 @@
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D35">
         <v>-0.02577116481204763</v>
@@ -3578,7 +3958,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D36">
         <v>-0.6405745998250554</v>
@@ -3604,7 +3984,7 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37">
         <v>0.8012323856566461</v>
@@ -3630,7 +4010,7 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38">
         <v>0.9492282876055838</v>
@@ -3656,7 +4036,7 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39">
         <v>0.6146641253020901</v>
@@ -3682,7 +4062,7 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D40">
         <v>-0.2850894140433184</v>
@@ -3708,7 +4088,7 @@
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D41">
         <v>-0.6031875208407139</v>
@@ -3734,7 +4114,7 @@
         <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D42">
         <v>1.232677313740137</v>
@@ -3760,7 +4140,7 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D43">
         <v>0.1222786302860112</v>
@@ -3786,7 +4166,7 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D44">
         <v>0.5037142975423412</v>
@@ -3812,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D45">
         <v>0.4946477615178588</v>
@@ -3838,7 +4218,7 @@
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D46">
         <v>0.06106940471735506</v>
@@ -3864,7 +4244,7 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D47">
         <v>-0.5080868026264761</v>
@@ -3890,7 +4270,7 @@
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -3901,7 +4281,7 @@
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49">
         <v>0.1725873022974022</v>
@@ -3927,7 +4307,7 @@
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D50">
         <v>-0.301842907985355</v>
@@ -3953,7 +4333,7 @@
         <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -3964,7 +4344,7 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D52">
         <v>-1.752667119028769</v>
@@ -3990,7 +4370,7 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D53">
         <v>0.2467393006635782</v>
@@ -4016,7 +4396,7 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54">
         <v>0.8177951052340048</v>
@@ -4042,7 +4422,7 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D55">
         <v>0.8382182385803767</v>
@@ -4068,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D56">
         <v>0.5234551665087729</v>
@@ -4094,7 +4474,7 @@
         <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D57">
         <v>-2.049102833279507</v>
@@ -4120,7 +4500,7 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58">
         <v>1.314765285259702</v>
@@ -4146,7 +4526,7 @@
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D59">
         <v>-1.771108985484543</v>
@@ -4172,7 +4552,7 @@
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D60">
         <v>-1.429778194779803</v>
@@ -4198,7 +4578,7 @@
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -4209,7 +4589,7 @@
         <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D62">
         <v>-0.307163068269531</v>
@@ -4235,7 +4615,7 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D63">
         <v>-0.968774017440613</v>
@@ -4261,7 +4641,7 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D64">
         <v>-0.3180865021614261</v>
@@ -4287,7 +4667,7 @@
         <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D65">
         <v>-0.5703905010013278</v>
@@ -4313,7 +4693,7 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D66">
         <v>-0.6298514028553761</v>
@@ -4339,7 +4719,7 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67">
         <v>-0.8061723903483715</v>
@@ -4365,7 +4745,7 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D68">
         <v>-0.3616712956849437</v>
@@ -4391,7 +4771,7 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D69">
         <v>0.07444513953919622</v>
@@ -4417,7 +4797,7 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D70">
         <v>1.155873010870637</v>
@@ -4443,7 +4823,7 @@
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D71">
         <v>-0.8869893850340613</v>
@@ -4469,7 +4849,7 @@
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -4480,7 +4860,7 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D73">
         <v>0.172246362207593</v>
@@ -4506,7 +4886,7 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D74">
         <v>1.146665694860658</v>
@@ -4532,7 +4912,7 @@
         <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D75">
         <v>-0.1168279932989959</v>
@@ -4558,7 +4938,7 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D76">
         <v>0.7189813887350064</v>
@@ -4584,7 +4964,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D77">
         <v>1.475659961011979</v>
@@ -4610,7 +4990,7 @@
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D78">
         <v>-0.9058809822050538</v>
@@ -4636,7 +5016,7 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D79">
         <v>0.767677142881948</v>
@@ -4662,7 +5042,7 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D80">
         <v>0.2319023658857199</v>
@@ -4688,7 +5068,7 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D81">
         <v>-1.284738051706735</v>
@@ -4714,7 +5094,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D82">
         <v>1.147174436285578</v>
@@ -4740,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D83">
         <v>1.271661700671106</v>
@@ -4766,7 +5146,7 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D84">
         <v>0.5979699843586228</v>
@@ -4792,7 +5172,7 @@
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D85">
         <v>0.830906129188078</v>
@@ -4818,7 +5198,7 @@
         <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D86">
         <v>-0.1636441297373128</v>
@@ -4844,7 +5224,7 @@
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D87">
         <v>0.6945917445816969</v>
@@ -4870,7 +5250,7 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D88">
         <v>0.2480106836223198</v>
@@ -4896,7 +5276,7 @@
         <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D89">
         <v>0.08064811654860106</v>
@@ -4922,7 +5302,7 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D90">
         <v>-0.9780118071351053</v>
@@ -4948,7 +5328,7 @@
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D91">
         <v>-0.4869225498056208</v>
@@ -4974,7 +5354,7 @@
         <v>14</v>
       </c>
       <c r="C92" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -4985,7 +5365,7 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D93">
         <v>0.4712359933849529</v>
@@ -5011,7 +5391,7 @@
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D94">
         <v>0.3506192928368125</v>
@@ -5037,7 +5417,7 @@
         <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D95">
         <v>0.903850812208177</v>
@@ -5063,7 +5443,7 @@
         <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D96">
         <v>-0.005786376953572689</v>
@@ -5089,7 +5469,7 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D97">
         <v>0.1587354548844314</v>
@@ -5115,7 +5495,7 @@
         <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D98">
         <v>-2.33309328961444</v>
@@ -5141,7 +5521,7 @@
         <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D99">
         <v>0.7940544713507275</v>
@@ -5167,7 +5547,7 @@
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D100">
         <v>0.3721578850811352</v>
@@ -5193,7 +5573,7 @@
         <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D101">
         <v>-0.4245868376755131</v>
@@ -5219,7 +5599,7 @@
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D102">
         <v>0.4846830297285377</v>
@@ -5245,7 +5625,7 @@
         <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D103">
         <v>0.2874772580724009</v>
@@ -5271,7 +5651,7 @@
         <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D104">
         <v>0.8079333191045459</v>
@@ -5297,7 +5677,7 @@
         <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D105">
         <v>0.5962863230725786</v>
@@ -5323,7 +5703,7 @@
         <v>9</v>
       </c>
       <c r="C106" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D106">
         <v>0.519790460000439</v>
@@ -5349,7 +5729,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D107">
         <v>-1.307456210334532</v>
@@ -5375,7 +5755,7 @@
         <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D108">
         <v>0.906860115624798</v>
@@ -5401,7 +5781,7 @@
         <v>10</v>
       </c>
       <c r="C109" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D109">
         <v>0.706554270652709</v>
@@ -5427,7 +5807,7 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D110">
         <v>0.6007580397260518</v>
@@ -5453,7 +5833,7 @@
         <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D111">
         <v>-1.092821380560519</v>
@@ -5479,7 +5859,7 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D112">
         <v>-0.7786925492884723</v>
@@ -5505,7 +5885,7 @@
         <v>10</v>
       </c>
       <c r="C113" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D113">
         <v>0.008791029014420129</v>
@@ -5531,7 +5911,7 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D114">
         <v>0.4274454383844277</v>
@@ -5557,7 +5937,7 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D115">
         <v>-2.052740539446993</v>
@@ -5583,7 +5963,7 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D116">
         <v>-1.782913960586113</v>
@@ -5609,7 +5989,7 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D117">
         <v>-0.259535019936775</v>

--- a/segmentation/segmentation_results.xlsx
+++ b/segmentation/segmentation_results.xlsx
@@ -21,14 +21,15 @@
     <sheet name="S5 性別" sheetId="12" r:id="rId12"/>
     <sheet name="S5 職業" sheetId="13" r:id="rId13"/>
     <sheet name="S5 年齢層" sheetId="14" r:id="rId14"/>
-    <sheet name="回答者別 所属" sheetId="15" r:id="rId15"/>
+    <sheet name="S5 撮影頻度" sheetId="15" r:id="rId15"/>
+    <sheet name="回答者別 所属" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="105">
   <si>
     <t>n</t>
   </si>
@@ -3082,6 +3083,594 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4">
+        <v>0.4421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5">
+        <v>63.3303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>19</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0.556</v>
+      </c>
+      <c r="D22">
+        <v>0.278</v>
+      </c>
+      <c r="E22">
+        <v>0.167</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0.025</v>
+      </c>
+      <c r="E23">
+        <v>0.475</v>
+      </c>
+      <c r="F23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0.143</v>
+      </c>
+      <c r="E24">
+        <v>0.619</v>
+      </c>
+      <c r="F24">
+        <v>0.238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0.125</v>
+      </c>
+      <c r="D25">
+        <v>0.208</v>
+      </c>
+      <c r="E25">
+        <v>0.5</v>
+      </c>
+      <c r="F25">
+        <v>0.167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0.4</v>
+      </c>
+      <c r="F26">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>6.22</v>
+      </c>
+      <c r="C32">
+        <v>2.05</v>
+      </c>
+      <c r="D32">
+        <v>-2.68</v>
+      </c>
+      <c r="E32">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <v>-2.95</v>
+      </c>
+      <c r="C33">
+        <v>-2.48</v>
+      </c>
+      <c r="D33">
+        <v>0.34</v>
+      </c>
+      <c r="E33">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34">
+        <v>-1.89</v>
+      </c>
+      <c r="C34">
+        <v>0.2</v>
+      </c>
+      <c r="D34">
+        <v>1.7</v>
+      </c>
+      <c r="E34">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>0.08</v>
+      </c>
+      <c r="C35">
+        <v>1.3</v>
+      </c>
+      <c r="D35">
+        <v>0.52</v>
+      </c>
+      <c r="E35">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36">
+        <v>-0.85</v>
+      </c>
+      <c r="C36">
+        <v>-0.88</v>
+      </c>
+      <c r="D36">
+        <v>-0.25</v>
+      </c>
+      <c r="E36">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0.7772</v>
+      </c>
+      <c r="D42">
+        <v>0.1428</v>
+      </c>
+      <c r="E42">
+        <v>0.0235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>0.0306</v>
+      </c>
+      <c r="C43">
+        <v>0.2359</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>0.0164</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>0.8884</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/segmentation/segmentation_results.xlsx
+++ b/segmentation/segmentation_results.xlsx
@@ -22,14 +22,18 @@
     <sheet name="S5 職業" sheetId="13" r:id="rId13"/>
     <sheet name="S5 年齢層" sheetId="14" r:id="rId14"/>
     <sheet name="S5 撮影頻度" sheetId="15" r:id="rId15"/>
-    <sheet name="回答者別 所属" sheetId="16" r:id="rId16"/>
+    <sheet name="S6 頻度×体験タイプ" sheetId="16" r:id="rId16"/>
+    <sheet name="S6 頻度×性別" sheetId="17" r:id="rId17"/>
+    <sheet name="S6 頻度×職業" sheetId="18" r:id="rId18"/>
+    <sheet name="S6 頻度×年齢層" sheetId="19" r:id="rId19"/>
+    <sheet name="回答者別 所属" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="105">
   <si>
     <t>n</t>
   </si>
@@ -325,6 +329,9 @@
     <t>23歳以上</t>
   </si>
   <si>
+    <t>撮影頻度</t>
+  </si>
+  <si>
     <t>回答No</t>
   </si>
   <si>
@@ -341,9 +348,6 @@
   </si>
   <si>
     <t>目的軸2 共有・楽しみ</t>
-  </si>
-  <si>
-    <t>撮影頻度</t>
   </si>
 </sst>
 </file>
@@ -3671,2929 +3675,1817 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3">
+        <v>0.9939</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4">
+        <v>0.1072</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5">
+        <v>3.7263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.125</v>
+      </c>
+      <c r="C22">
+        <v>0.375</v>
+      </c>
+      <c r="D22">
+        <v>0.25</v>
+      </c>
+      <c r="E22">
+        <v>0.125</v>
+      </c>
+      <c r="F22">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>0.154</v>
+      </c>
+      <c r="C23">
+        <v>0.231</v>
+      </c>
+      <c r="D23">
+        <v>0.462</v>
+      </c>
+      <c r="E23">
+        <v>0.077</v>
+      </c>
+      <c r="F23">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>0.286</v>
+      </c>
+      <c r="C24">
+        <v>0.214</v>
+      </c>
+      <c r="D24">
+        <v>0.357</v>
+      </c>
+      <c r="E24">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="F24">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>0.245</v>
+      </c>
+      <c r="C25">
+        <v>0.245</v>
+      </c>
+      <c r="D25">
+        <v>0.347</v>
+      </c>
+      <c r="E25">
+        <v>0.143</v>
+      </c>
+      <c r="F25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>0.281</v>
+      </c>
+      <c r="C26">
+        <v>0.219</v>
+      </c>
+      <c r="D26">
+        <v>0.281</v>
+      </c>
+      <c r="E26">
+        <v>0.094</v>
+      </c>
+      <c r="F26">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
         <v>81</v>
       </c>
-      <c r="D3">
-        <v>-0.5574747128376729</v>
-      </c>
-      <c r="E3">
-        <v>0.09079128689885294</v>
-      </c>
-      <c r="F3">
-        <v>0.3815229241509477</v>
-      </c>
-      <c r="G3">
-        <v>0.1452879090615219</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4">
-        <v>-0.1299976216298829</v>
-      </c>
-      <c r="E4">
-        <v>0.7264908971373215</v>
-      </c>
-      <c r="F4">
-        <v>0.1734068889288403</v>
-      </c>
-      <c r="G4">
-        <v>1.397438665939546</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E31" t="s">
         <v>82</v>
       </c>
-      <c r="D5">
-        <v>-0.1746485687842852</v>
-      </c>
-      <c r="E5">
-        <v>-0.3440516629722525</v>
-      </c>
-      <c r="F5">
-        <v>0.3246516518557641</v>
-      </c>
-      <c r="G5">
-        <v>-0.1894724763615691</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>-0.73</v>
+      </c>
+      <c r="C32">
+        <v>1.06</v>
+      </c>
+      <c r="D32">
+        <v>-0.43</v>
+      </c>
+      <c r="E32">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>-0.78</v>
+      </c>
+      <c r="C33">
+        <v>-0.08</v>
+      </c>
+      <c r="D33">
+        <v>1.06</v>
+      </c>
+      <c r="E33">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.42</v>
+      </c>
+      <c r="C34">
+        <v>-0.25</v>
+      </c>
+      <c r="D34">
+        <v>0.19</v>
+      </c>
+      <c r="E34">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>-0.2</v>
+      </c>
+      <c r="C35">
+        <v>-0.2</v>
+      </c>
+      <c r="D35">
+        <v>-0.13</v>
+      </c>
+      <c r="E35">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>0.87</v>
+      </c>
+      <c r="C36">
+        <v>-0.13</v>
+      </c>
+      <c r="D36">
+        <v>-0.51</v>
+      </c>
+      <c r="E36">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
         <v>79</v>
-      </c>
-      <c r="D6">
-        <v>-0.5447978709999376</v>
-      </c>
-      <c r="E6">
-        <v>-0.08939013470924551</v>
-      </c>
-      <c r="F6">
-        <v>0.2022956400079265</v>
-      </c>
-      <c r="G6">
-        <v>1.223239809520513</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8">
-        <v>-1.023645559773101</v>
-      </c>
-      <c r="E8">
-        <v>-0.1950571185501851</v>
-      </c>
-      <c r="F8">
-        <v>0.2330175199311118</v>
-      </c>
-      <c r="G8">
-        <v>-0.3673743700879396</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9">
-        <v>-0.1838781302108423</v>
-      </c>
-      <c r="E9">
-        <v>-0.1972755834591212</v>
-      </c>
-      <c r="F9">
-        <v>0.06460308398013685</v>
-      </c>
-      <c r="G9">
-        <v>0.9677108219141707</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10">
-        <v>0.3612939728313038</v>
-      </c>
-      <c r="E10">
-        <v>0.02011413855760352</v>
-      </c>
-      <c r="F10">
-        <v>-3.226229149704582</v>
-      </c>
-      <c r="G10">
-        <v>-2.124509303992919</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11">
-        <v>-0.3220542533230158</v>
-      </c>
-      <c r="E11">
-        <v>1.024869188951069</v>
-      </c>
-      <c r="F11">
-        <v>0.7078432807053865</v>
-      </c>
-      <c r="G11">
-        <v>-1.488788651187809</v>
-      </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>0.3439782907502662</v>
-      </c>
-      <c r="E12">
-        <v>-1.422201155199607</v>
-      </c>
-      <c r="F12">
-        <v>-2.596294526831652</v>
-      </c>
-      <c r="G12">
-        <v>-1.386678017632773</v>
-      </c>
-      <c r="H12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13">
-        <v>0.3900039728561599</v>
-      </c>
-      <c r="E13">
-        <v>-1.009954880633531</v>
-      </c>
-      <c r="F13">
-        <v>0.2515257194945251</v>
-      </c>
-      <c r="G13">
-        <v>0.6040350547969764</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14">
-        <v>0.09231223844119693</v>
-      </c>
-      <c r="E14">
-        <v>-1.913126750855901</v>
-      </c>
-      <c r="F14">
-        <v>0.4195104607768282</v>
-      </c>
-      <c r="G14">
-        <v>-0.2063313495368382</v>
-      </c>
-      <c r="H14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15">
-        <v>1.430304746738134</v>
-      </c>
-      <c r="E15">
-        <v>0.2067577064421887</v>
-      </c>
-      <c r="F15">
-        <v>0.2420360606761059</v>
-      </c>
-      <c r="G15">
-        <v>0.04669778550219194</v>
-      </c>
-      <c r="H15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16">
-        <v>1.01136348502193</v>
-      </c>
-      <c r="E16">
-        <v>-0.1748919691176447</v>
-      </c>
-      <c r="F16">
-        <v>-0.6760137149362867</v>
-      </c>
-      <c r="G16">
-        <v>1.47454894126003</v>
-      </c>
-      <c r="H16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17">
-        <v>-0.4998374252596787</v>
-      </c>
-      <c r="E17">
-        <v>0.7196278458589965</v>
-      </c>
-      <c r="F17">
-        <v>0.7350192701430732</v>
-      </c>
-      <c r="G17">
-        <v>-1.133811021071607</v>
-      </c>
-      <c r="H17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18">
-        <v>0.2607913482830148</v>
-      </c>
-      <c r="E18">
-        <v>0.7955004005631312</v>
-      </c>
-      <c r="F18">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G18">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19">
-        <v>1.350831670822532</v>
-      </c>
-      <c r="E19">
-        <v>-0.3014474608851019</v>
-      </c>
-      <c r="F19">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G19">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20">
-        <v>1.462652674166755</v>
-      </c>
-      <c r="E20">
-        <v>0.1292062937654839</v>
-      </c>
-      <c r="F20">
-        <v>1.182669041479662</v>
-      </c>
-      <c r="G20">
-        <v>-2.610202932287678</v>
-      </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21">
-        <v>-0.3498664855860121</v>
-      </c>
-      <c r="E21">
-        <v>-1.014723692154709</v>
-      </c>
-      <c r="F21">
-        <v>0.2873694988064842</v>
-      </c>
-      <c r="G21">
-        <v>0.3425808901444636</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22">
-        <v>-1.223955685244825</v>
-      </c>
-      <c r="E22">
-        <v>1.281142753952548</v>
-      </c>
-      <c r="F22">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G22">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23">
-        <v>0.5179070850451212</v>
-      </c>
-      <c r="E23">
-        <v>0.4675305835806728</v>
-      </c>
-      <c r="F23">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G23">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24">
-        <v>-0.05756116889432042</v>
-      </c>
-      <c r="E24">
-        <v>0.7586025642385782</v>
-      </c>
-      <c r="F24">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G24">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25">
-        <v>-0.7554598042702086</v>
-      </c>
-      <c r="E25">
-        <v>0.6567310996811981</v>
-      </c>
-      <c r="F25">
-        <v>0.1101881279311937</v>
-      </c>
-      <c r="G25">
-        <v>0.5457677115961386</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27">
-        <v>1.171836154418401</v>
-      </c>
-      <c r="E27">
-        <v>0.06521795499388564</v>
-      </c>
-      <c r="F27">
-        <v>0.5205990312330752</v>
-      </c>
-      <c r="G27">
-        <v>-0.3492924766326946</v>
-      </c>
-      <c r="H27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28">
-        <v>0.2448824796140681</v>
-      </c>
-      <c r="E28">
-        <v>-0.8168223413693565</v>
-      </c>
-      <c r="F28">
-        <v>-0.1298588224398975</v>
-      </c>
-      <c r="G28">
-        <v>1.826322047227112</v>
-      </c>
-      <c r="H28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29">
-        <v>1.120174839935586</v>
-      </c>
-      <c r="E29">
-        <v>-0.1126378239392984</v>
-      </c>
-      <c r="F29">
-        <v>0.2314944124786899</v>
-      </c>
-      <c r="G29">
-        <v>0.3742143590811108</v>
-      </c>
-      <c r="H29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30">
-        <v>-0.2195817119969808</v>
-      </c>
-      <c r="E30">
-        <v>0.4601841119489008</v>
-      </c>
-      <c r="F30">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G30">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31">
-        <v>-0.004578590777285951</v>
-      </c>
-      <c r="E31">
-        <v>0.1051330970640331</v>
-      </c>
-      <c r="F31">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G31">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32">
-        <v>-1.569471018290258</v>
-      </c>
-      <c r="E32">
-        <v>1.540057074870689</v>
-      </c>
-      <c r="F32">
-        <v>0.3146658554468746</v>
-      </c>
-      <c r="G32">
-        <v>-0.1896803163935274</v>
-      </c>
-      <c r="H32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33">
-        <v>-1.205124956539953</v>
-      </c>
-      <c r="E33">
-        <v>-0.2904509429746304</v>
-      </c>
-      <c r="F33">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G33">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34">
-        <v>-0.4511592700069666</v>
-      </c>
-      <c r="E34">
-        <v>-0.3093638801196507</v>
-      </c>
-      <c r="F34">
-        <v>0.893334646135399</v>
-      </c>
-      <c r="G34">
-        <v>-1.803362060322961</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35">
-        <v>-0.02577116481204763</v>
-      </c>
-      <c r="E35">
-        <v>1.048520780226261</v>
-      </c>
-      <c r="F35">
-        <v>0.3246516518557637</v>
-      </c>
-      <c r="G35">
-        <v>-0.1894724763615693</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36">
-        <v>-0.6405745998250554</v>
-      </c>
-      <c r="E36">
-        <v>0.7550907396172402</v>
-      </c>
-      <c r="F36">
-        <v>-0.8784616779254647</v>
-      </c>
-      <c r="G36">
-        <v>0.5051028971099536</v>
-      </c>
-      <c r="H36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37">
-        <v>0.8012323856566461</v>
-      </c>
-      <c r="E37">
-        <v>-0.402581899533012</v>
-      </c>
-      <c r="F37">
-        <v>-0.3184432829144211</v>
-      </c>
-      <c r="G37">
-        <v>1.001269756916364</v>
-      </c>
-      <c r="H37">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38">
-        <v>0.9492282876055838</v>
-      </c>
-      <c r="E38">
-        <v>-1.304449593025374</v>
-      </c>
-      <c r="F38">
-        <v>0.2420360606761059</v>
-      </c>
-      <c r="G38">
-        <v>0.04669778550219194</v>
-      </c>
-      <c r="H38">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39">
-        <v>0.6146641253020901</v>
-      </c>
-      <c r="E39">
-        <v>-0.5102473739885162</v>
-      </c>
-      <c r="F39">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G39">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40">
-        <v>-0.2850894140433184</v>
-      </c>
-      <c r="E40">
-        <v>1.308057906297319</v>
-      </c>
-      <c r="F40">
-        <v>0.6182892529975285</v>
-      </c>
-      <c r="G40">
-        <v>-1.016062501613756</v>
-      </c>
-      <c r="H40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>11</v>
       </c>
       <c r="C41" t="s">
         <v>80</v>
       </c>
-      <c r="D41">
-        <v>-0.6031875208407139</v>
-      </c>
-      <c r="E41">
-        <v>0.1333127524718746</v>
-      </c>
-      <c r="F41">
-        <v>0.6730575767583297</v>
-      </c>
-      <c r="G41">
-        <v>-0.9566833246737863</v>
-      </c>
-      <c r="H41">
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3">
+        <v>0.0506</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4">
+        <v>0.2848</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5">
+        <v>9.3277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>21</v>
+      </c>
+      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="E15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>14</v>
+      </c>
+      <c r="E16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0.25</v>
+      </c>
+      <c r="D22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0.615</v>
+      </c>
+      <c r="D23">
+        <v>0.385</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0.143</v>
+      </c>
+      <c r="D24">
+        <v>0.857</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0.429</v>
+      </c>
+      <c r="D25">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>0.031</v>
+      </c>
+      <c r="C26">
+        <v>0.531</v>
+      </c>
+      <c r="D26">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>1.09</v>
+      </c>
+      <c r="C32">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>-1.39</v>
+      </c>
+      <c r="C33">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>2.35</v>
+      </c>
+      <c r="C34">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>0.12</v>
+      </c>
+      <c r="C35">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>-1.49</v>
+      </c>
+      <c r="C36">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <v>0.217</v>
+      </c>
+      <c r="C44">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3">
+        <v>0.9236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4">
+        <v>0.1009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5">
+        <v>1.1811</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.875</v>
+      </c>
+      <c r="C22">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>0.923</v>
+      </c>
+      <c r="C23">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>0.857</v>
+      </c>
+      <c r="C24">
+        <v>0.143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>0.878</v>
+      </c>
+      <c r="C25">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="C26">
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>0.11</v>
+      </c>
+      <c r="C32">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>0.68</v>
+      </c>
+      <c r="C33">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>-0.06</v>
+      </c>
+      <c r="C34">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>0.41</v>
+      </c>
+      <c r="C35">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>-0.96</v>
+      </c>
+      <c r="C36">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3">
+        <v>0.0174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4">
+        <v>0.2509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5">
+        <v>21.9118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
-        <v>80</v>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.125</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <v>0.25</v>
+      </c>
+      <c r="E22">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>0.231</v>
+      </c>
+      <c r="C23">
+        <v>0.308</v>
+      </c>
+      <c r="D23">
+        <v>0.231</v>
+      </c>
+      <c r="E23">
+        <v>0.231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="C24">
+        <v>0.357</v>
+      </c>
+      <c r="D24">
+        <v>0.5</v>
+      </c>
+      <c r="E24">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>0.204</v>
+      </c>
+      <c r="C25">
+        <v>0.224</v>
+      </c>
+      <c r="D25">
+        <v>0.306</v>
+      </c>
+      <c r="E25">
+        <v>0.265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>0.406</v>
+      </c>
+      <c r="C26">
+        <v>0.25</v>
+      </c>
+      <c r="D26">
+        <v>0.031</v>
+      </c>
+      <c r="E26">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>-0.8</v>
+      </c>
+      <c r="C32">
+        <v>1.47</v>
+      </c>
+      <c r="D32">
+        <v>0.06</v>
+      </c>
+      <c r="E32">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>-0.09</v>
+      </c>
+      <c r="C33">
+        <v>0.27</v>
+      </c>
+      <c r="D33">
+        <v>-0.09</v>
+      </c>
+      <c r="E33">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>-1.58</v>
+      </c>
+      <c r="C34">
+        <v>0.73</v>
+      </c>
+      <c r="D34">
+        <v>2.41</v>
+      </c>
+      <c r="E34">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>-0.8</v>
+      </c>
+      <c r="C35">
+        <v>-1.06</v>
+      </c>
+      <c r="D35">
+        <v>1.39</v>
+      </c>
+      <c r="E35">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>2.56</v>
+      </c>
+      <c r="C36">
+        <v>-0.38</v>
+      </c>
+      <c r="D36">
+        <v>-3.26</v>
+      </c>
+      <c r="E36">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>1.232677313740137</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>0.2321503562222653</v>
-      </c>
-      <c r="F42">
-        <v>0.2873694988064842</v>
-      </c>
-      <c r="G42">
-        <v>0.3425808901444636</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>0.1222786302860112</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>-0.3606368993068123</v>
-      </c>
-      <c r="F43">
-        <v>0.1734068889288418</v>
-      </c>
-      <c r="G43">
-        <v>1.397438665939542</v>
-      </c>
-      <c r="H43">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>0.5037142975423412</v>
+        <v>0.7086</v>
       </c>
       <c r="E44">
-        <v>-0.02977427884725369</v>
-      </c>
-      <c r="F44">
-        <v>0.5727042090464712</v>
-      </c>
-      <c r="G44">
-        <v>-0.5941193912957242</v>
-      </c>
-      <c r="H44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>0.4946477615178588</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>0.4572055468364684</v>
-      </c>
-      <c r="F45">
-        <v>0.09989286381015486</v>
-      </c>
-      <c r="G45">
-        <v>0.8184767454407612</v>
-      </c>
-      <c r="H45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>0.287</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0.06106940471735506</v>
+        <v>0.0112</v>
       </c>
       <c r="E46">
-        <v>0.08411433707751106</v>
-      </c>
-      <c r="F46">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G46">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47">
-        <v>-0.5080868026264761</v>
-      </c>
-      <c r="E47">
-        <v>0.9658882465728784</v>
-      </c>
-      <c r="F47">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G47">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49">
-        <v>0.1725873022974022</v>
-      </c>
-      <c r="E49">
-        <v>0.354621530543582</v>
-      </c>
-      <c r="F49">
-        <v>1.140393990225938</v>
-      </c>
-      <c r="G49">
-        <v>-2.078253485797624</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50">
-        <v>-0.301842907985355</v>
-      </c>
-      <c r="E50">
-        <v>-0.2941489461860824</v>
-      </c>
-      <c r="F50">
-        <v>0.288416999272182</v>
-      </c>
-      <c r="G50">
-        <v>-0.6627759831831712</v>
-      </c>
-      <c r="H50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52">
-        <v>-1.752667119028769</v>
-      </c>
-      <c r="E52">
-        <v>-0.6268197064374335</v>
-      </c>
-      <c r="F52">
-        <v>0.7350192701430732</v>
-      </c>
-      <c r="G52">
-        <v>-1.133811021071607</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53">
-        <v>0.2467393006635782</v>
-      </c>
-      <c r="E53">
-        <v>-0.07526538499694292</v>
-      </c>
-      <c r="F53">
-        <v>0.7078432807053868</v>
-      </c>
-      <c r="G53">
-        <v>-1.488788651187809</v>
-      </c>
-      <c r="H53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54">
-        <v>0.8177951052340048</v>
-      </c>
-      <c r="E54">
-        <v>0.4464834087844466</v>
-      </c>
-      <c r="F54">
-        <v>0.06460308398013674</v>
-      </c>
-      <c r="G54">
-        <v>0.9677108219141703</v>
-      </c>
-      <c r="H54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55">
-        <v>0.8382182385803767</v>
-      </c>
-      <c r="E55">
-        <v>-0.0272424016828803</v>
-      </c>
-      <c r="F55">
-        <v>0.3246516518557637</v>
-      </c>
-      <c r="G55">
-        <v>-0.1894724763615693</v>
-      </c>
-      <c r="H55">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
-        <v>82</v>
-      </c>
-      <c r="D56">
-        <v>0.5234551665087729</v>
-      </c>
-      <c r="E56">
-        <v>0.5972957091695618</v>
-      </c>
-      <c r="F56">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G56">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57">
-        <v>-2.049102833279507</v>
-      </c>
-      <c r="E57">
-        <v>1.52245707306025</v>
-      </c>
-      <c r="F57">
-        <v>0.3146658554468746</v>
-      </c>
-      <c r="G57">
-        <v>-0.1896803163935274</v>
-      </c>
-      <c r="H57">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58">
-        <v>1.314765285259702</v>
-      </c>
-      <c r="E58">
-        <v>-0.9698150231558224</v>
-      </c>
-      <c r="F58">
-        <v>-0.2660049921224907</v>
-      </c>
-      <c r="G58">
-        <v>0.3958216343954712</v>
-      </c>
-      <c r="H58">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59">
-        <v>-1.771108985484543</v>
-      </c>
-      <c r="E59">
-        <v>0.1106798403409976</v>
-      </c>
-      <c r="F59">
-        <v>0.0001184990954326288</v>
-      </c>
-      <c r="G59">
-        <v>1.509162063712226</v>
-      </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60">
-        <v>-1.429778194779803</v>
-      </c>
-      <c r="E60">
-        <v>1.02673133312414</v>
-      </c>
-      <c r="F60">
-        <v>0.3146658554468746</v>
-      </c>
-      <c r="G60">
-        <v>-0.1896803163935274</v>
-      </c>
-      <c r="H60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62">
-        <v>-0.307163068269531</v>
-      </c>
-      <c r="E62">
-        <v>-0.723313493836271</v>
-      </c>
-      <c r="F62">
-        <v>0.5727042090464712</v>
-      </c>
-      <c r="G62">
-        <v>-0.5941193912957242</v>
-      </c>
-      <c r="H62">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63">
-        <v>-0.968774017440613</v>
-      </c>
-      <c r="E63">
-        <v>0.2490921774505762</v>
-      </c>
-      <c r="F63">
-        <v>0.7078432807053868</v>
-      </c>
-      <c r="G63">
-        <v>-1.488788651187809</v>
-      </c>
-      <c r="H63">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" t="s">
-        <v>82</v>
-      </c>
-      <c r="D64">
-        <v>-0.3180865021614261</v>
-      </c>
-      <c r="E64">
-        <v>-0.2157917893235479</v>
-      </c>
-      <c r="F64">
-        <v>-0.2287358778058282</v>
-      </c>
-      <c r="G64">
-        <v>0.7194136361301139</v>
-      </c>
-      <c r="H64">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" t="s">
-        <v>83</v>
-      </c>
-      <c r="D65">
-        <v>-0.5703905010013278</v>
-      </c>
-      <c r="E65">
-        <v>0.4267255524380323</v>
-      </c>
-      <c r="F65">
-        <v>1.182669041479662</v>
-      </c>
-      <c r="G65">
-        <v>-2.610202932287678</v>
-      </c>
-      <c r="H65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66">
-        <v>-0.6298514028553761</v>
-      </c>
-      <c r="E66">
-        <v>1.092133285726496</v>
-      </c>
-      <c r="F66">
-        <v>-0.5422870210645181</v>
-      </c>
-      <c r="G66">
-        <v>1.388876534891805</v>
-      </c>
-      <c r="H66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" t="s">
-        <v>81</v>
-      </c>
-      <c r="D67">
-        <v>-0.8061723903483715</v>
-      </c>
-      <c r="E67">
-        <v>1.04653588195966</v>
-      </c>
-      <c r="F67">
-        <v>-9.128984631952006</v>
-      </c>
-      <c r="G67">
-        <v>-1.960440124448817</v>
-      </c>
-      <c r="H67">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" t="s">
-        <v>82</v>
-      </c>
-      <c r="D68">
-        <v>-0.3616712956849437</v>
-      </c>
-      <c r="E68">
-        <v>-1.174178520217661</v>
-      </c>
-      <c r="F68">
-        <v>-3.253405139142266</v>
-      </c>
-      <c r="G68">
-        <v>-2.47948693410912</v>
-      </c>
-      <c r="H68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" t="s">
-        <v>83</v>
-      </c>
-      <c r="D69">
-        <v>0.07444513953919622</v>
-      </c>
-      <c r="E69">
-        <v>-1.152308147923284</v>
-      </c>
-      <c r="F69">
-        <v>0.06460308398013674</v>
-      </c>
-      <c r="G69">
-        <v>0.9677108219141703</v>
-      </c>
-      <c r="H69">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" t="s">
-        <v>79</v>
-      </c>
-      <c r="D70">
-        <v>1.155873010870637</v>
-      </c>
-      <c r="E70">
-        <v>0.02827412603082538</v>
-      </c>
-      <c r="F70">
-        <v>0.2873694988064842</v>
-      </c>
-      <c r="G70">
-        <v>0.3425808901444636</v>
-      </c>
-      <c r="H70">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" t="s">
-        <v>81</v>
-      </c>
-      <c r="D71">
-        <v>-0.8869893850340613</v>
-      </c>
-      <c r="E71">
-        <v>1.094208413729989</v>
-      </c>
-      <c r="F71">
-        <v>0.8107190549557417</v>
-      </c>
-      <c r="G71">
-        <v>-1.5671917984592</v>
-      </c>
-      <c r="H71">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73">
-        <v>0.172246362207593</v>
-      </c>
-      <c r="E73">
-        <v>0.422777888772521</v>
-      </c>
-      <c r="F73">
-        <v>-0.9132473818725217</v>
-      </c>
-      <c r="G73">
-        <v>1.037208223623976</v>
-      </c>
-      <c r="H73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74">
-        <v>1.146665694860658</v>
-      </c>
-      <c r="E74">
-        <v>0.5009448945229221</v>
-      </c>
-      <c r="F74">
-        <v>0.2314944124786899</v>
-      </c>
-      <c r="G74">
-        <v>0.3742143590811108</v>
-      </c>
-      <c r="H74">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" t="s">
-        <v>81</v>
-      </c>
-      <c r="D75">
-        <v>-0.1168279932989959</v>
-      </c>
-      <c r="E75">
-        <v>-1.206110989211106</v>
-      </c>
-      <c r="F75">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G75">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H75">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" t="s">
-        <v>80</v>
-      </c>
-      <c r="D76">
-        <v>0.7189813887350064</v>
-      </c>
-      <c r="E76">
-        <v>0.4591797336744849</v>
-      </c>
-      <c r="F76">
-        <v>0.2022956400079261</v>
-      </c>
-      <c r="G76">
-        <v>1.223239809520513</v>
-      </c>
-      <c r="H76">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77">
-        <v>1.475659961011979</v>
-      </c>
-      <c r="E77">
-        <v>0.572556373306108</v>
-      </c>
-      <c r="F77">
-        <v>0.2600731421660941</v>
-      </c>
-      <c r="G77">
-        <v>0.8748420966824551</v>
-      </c>
-      <c r="H77">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78">
-        <v>-0.9058809822050538</v>
-      </c>
-      <c r="E78">
-        <v>-0.4034883207264326</v>
-      </c>
-      <c r="F78">
-        <v>0.08634387553028583</v>
-      </c>
-      <c r="G78">
-        <v>1.251692926007131</v>
-      </c>
-      <c r="H78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" t="s">
-        <v>80</v>
-      </c>
-      <c r="D79">
-        <v>0.767677142881948</v>
-      </c>
-      <c r="E79">
-        <v>0.6165935536653225</v>
-      </c>
-      <c r="F79">
-        <v>-0.6380261783104061</v>
-      </c>
-      <c r="G79">
-        <v>1.12292968266167</v>
-      </c>
-      <c r="H79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" t="s">
-        <v>80</v>
-      </c>
-      <c r="D80">
-        <v>0.2319023658857199</v>
-      </c>
-      <c r="E80">
-        <v>0.6175353957100703</v>
-      </c>
-      <c r="F80">
-        <v>0.3296445500602083</v>
-      </c>
-      <c r="G80">
-        <v>-0.1893685563455903</v>
-      </c>
-      <c r="H80">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" t="s">
-        <v>80</v>
-      </c>
-      <c r="D81">
-        <v>-1.284738051706735</v>
-      </c>
-      <c r="E81">
-        <v>1.141091709364682</v>
-      </c>
-      <c r="F81">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G81">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H81">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
-        <v>81</v>
-      </c>
-      <c r="D82">
-        <v>1.147174436285578</v>
-      </c>
-      <c r="E82">
-        <v>-0.351972635656601</v>
-      </c>
-      <c r="F82">
-        <v>0.2314944124786899</v>
-      </c>
-      <c r="G82">
-        <v>0.3742143590811108</v>
-      </c>
-      <c r="H82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>79</v>
-      </c>
-      <c r="D83">
-        <v>1.271661700671106</v>
-      </c>
-      <c r="E83">
-        <v>-0.6495060670278778</v>
-      </c>
-      <c r="F83">
-        <v>0.2600731421660941</v>
-      </c>
-      <c r="G83">
-        <v>0.8748420966824551</v>
-      </c>
-      <c r="H83">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>81</v>
-      </c>
-      <c r="D84">
-        <v>0.5979699843586228</v>
-      </c>
-      <c r="E84">
-        <v>-1.028553418574162</v>
-      </c>
-      <c r="F84">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G84">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" t="s">
-        <v>79</v>
-      </c>
-      <c r="D85">
-        <v>0.830906129188078</v>
-      </c>
-      <c r="E85">
-        <v>0.01390939603257811</v>
-      </c>
-      <c r="F85">
-        <v>0.288416999272182</v>
-      </c>
-      <c r="G85">
-        <v>-0.6627759831831712</v>
-      </c>
-      <c r="H85">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" t="s">
-        <v>81</v>
-      </c>
-      <c r="D86">
-        <v>-0.1636441297373128</v>
-      </c>
-      <c r="E86">
-        <v>-1.240846171586163</v>
-      </c>
-      <c r="F86">
-        <v>0.7078432807053868</v>
-      </c>
-      <c r="G86">
-        <v>-1.488788651187809</v>
-      </c>
-      <c r="H86">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" t="s">
-        <v>79</v>
-      </c>
-      <c r="D87">
-        <v>0.6945917445816969</v>
-      </c>
-      <c r="E87">
-        <v>-0.04167965907273542</v>
-      </c>
-      <c r="F87">
-        <v>0.6182892529975285</v>
-      </c>
-      <c r="G87">
-        <v>-1.016062501613756</v>
-      </c>
-      <c r="H87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" t="s">
-        <v>80</v>
-      </c>
-      <c r="D88">
-        <v>0.2480106836223198</v>
-      </c>
-      <c r="E88">
-        <v>0.6119122906722967</v>
-      </c>
-      <c r="F88">
-        <v>0.288416999272182</v>
-      </c>
-      <c r="G88">
-        <v>-0.6627759831831712</v>
-      </c>
-      <c r="H88">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>12</v>
-      </c>
-      <c r="C89" t="s">
-        <v>79</v>
-      </c>
-      <c r="D89">
-        <v>0.08064811654860106</v>
-      </c>
-      <c r="E89">
-        <v>-1.509654325175251</v>
-      </c>
-      <c r="F89">
-        <v>0.2314944124786899</v>
-      </c>
-      <c r="G89">
-        <v>0.3742143590811108</v>
-      </c>
-      <c r="H89">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" t="s">
-        <v>80</v>
-      </c>
-      <c r="D90">
-        <v>-0.9780118071351053</v>
-      </c>
-      <c r="E90">
-        <v>1.566639690605868</v>
-      </c>
-      <c r="F90">
-        <v>0.3569409067005985</v>
-      </c>
-      <c r="G90">
-        <v>-0.7216297628835812</v>
-      </c>
-      <c r="H90">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91" t="s">
-        <v>80</v>
-      </c>
-      <c r="D91">
-        <v>-0.4869225498056208</v>
-      </c>
-      <c r="E91">
-        <v>-0.8175848812058564</v>
-      </c>
-      <c r="F91">
-        <v>0.1660609874243442</v>
-      </c>
-      <c r="G91">
-        <v>0.7499363026989111</v>
-      </c>
-      <c r="H91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>14</v>
-      </c>
-      <c r="C92" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" t="s">
-        <v>82</v>
-      </c>
-      <c r="D93">
-        <v>0.4712359933849529</v>
-      </c>
-      <c r="E93">
-        <v>0.6546825283354375</v>
-      </c>
-      <c r="F93">
-        <v>-2.221321819121608</v>
-      </c>
-      <c r="G93">
-        <v>-0.8667968714843786</v>
-      </c>
-      <c r="H93">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" t="s">
-        <v>80</v>
-      </c>
-      <c r="D94">
-        <v>0.3506192928368125</v>
-      </c>
-      <c r="E94">
-        <v>-1.144042907052204</v>
-      </c>
-      <c r="F94">
-        <v>-0.8693188579642599</v>
-      </c>
-      <c r="G94">
-        <v>2.304156675479724</v>
-      </c>
-      <c r="H94">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95">
-        <v>0.903850812208177</v>
-      </c>
-      <c r="E95">
-        <v>0.5256465210136831</v>
-      </c>
-      <c r="F95">
-        <v>0.8469537075393234</v>
-      </c>
-      <c r="G95">
-        <v>-1.093888291637598</v>
-      </c>
-      <c r="H95">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" t="s">
-        <v>81</v>
-      </c>
-      <c r="D96">
-        <v>-0.005786376953572689</v>
-      </c>
-      <c r="E96">
-        <v>-0.6624863551260076</v>
-      </c>
-      <c r="F96">
-        <v>-0.650754713907153</v>
-      </c>
-      <c r="G96">
-        <v>0.5790507370244538</v>
-      </c>
-      <c r="H96">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" t="s">
-        <v>80</v>
-      </c>
-      <c r="D97">
-        <v>0.1587354548844314</v>
-      </c>
-      <c r="E97">
-        <v>-0.2108396901132833</v>
-      </c>
-      <c r="F97">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G97">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H97">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98" t="s">
-        <v>79</v>
-      </c>
-      <c r="D98">
-        <v>-2.33309328961444</v>
-      </c>
-      <c r="E98">
-        <v>-0.4961044670082163</v>
-      </c>
-      <c r="F98">
-        <v>0.3992159579543226</v>
-      </c>
-      <c r="G98">
-        <v>-1.253579209373635</v>
-      </c>
-      <c r="H98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" t="s">
-        <v>81</v>
-      </c>
-      <c r="D99">
-        <v>0.7940544713507275</v>
-      </c>
-      <c r="E99">
-        <v>0.4395585311086999</v>
-      </c>
-      <c r="F99">
-        <v>0.04291155887133363</v>
-      </c>
-      <c r="G99">
-        <v>1.345905633338301</v>
-      </c>
-      <c r="H99">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" t="s">
-        <v>79</v>
-      </c>
-      <c r="D100">
-        <v>0.3721578850811352</v>
-      </c>
-      <c r="E100">
-        <v>0.5036927724238125</v>
-      </c>
-      <c r="F100">
-        <v>0.1101881279311937</v>
-      </c>
-      <c r="G100">
-        <v>0.5457677115961386</v>
-      </c>
-      <c r="H100">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101" t="s">
-        <v>79</v>
-      </c>
-      <c r="D101">
-        <v>-0.4245868376755131</v>
-      </c>
-      <c r="E101">
-        <v>0.3420936808625378</v>
-      </c>
-      <c r="F101">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G101">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H101">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102" t="s">
-        <v>12</v>
-      </c>
-      <c r="C102" t="s">
-        <v>80</v>
-      </c>
-      <c r="D102">
-        <v>0.4846830297285377</v>
-      </c>
-      <c r="E102">
-        <v>-1.397860970286455</v>
-      </c>
-      <c r="F102">
-        <v>0.6780379652042521</v>
-      </c>
-      <c r="G102">
-        <v>-0.6063821331740676</v>
-      </c>
-      <c r="H102">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" t="s">
-        <v>81</v>
-      </c>
-      <c r="D103">
-        <v>0.2874772580724009</v>
-      </c>
-      <c r="E103">
-        <v>-0.1519867367524503</v>
-      </c>
-      <c r="F103">
-        <v>0.09718142701112946</v>
-      </c>
-      <c r="G103">
-        <v>0.9522327010422177</v>
-      </c>
-      <c r="H103">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" t="s">
-        <v>79</v>
-      </c>
-      <c r="D104">
-        <v>0.8079333191045459</v>
-      </c>
-      <c r="E104">
-        <v>-1.165971131733398</v>
-      </c>
-      <c r="F104">
-        <v>-0.674598966308061</v>
-      </c>
-      <c r="G104">
-        <v>1.284975951435447</v>
-      </c>
-      <c r="H104">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" t="s">
-        <v>81</v>
-      </c>
-      <c r="D105">
-        <v>0.5962863230725786</v>
-      </c>
-      <c r="E105">
-        <v>0.3184150931318233</v>
-      </c>
-      <c r="F105">
-        <v>0.2022956400079261</v>
-      </c>
-      <c r="G105">
-        <v>1.223239809520513</v>
-      </c>
-      <c r="H105">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
-        <v>81</v>
-      </c>
-      <c r="D106">
-        <v>0.519790460000439</v>
-      </c>
-      <c r="E106">
-        <v>0.238412613948167</v>
-      </c>
-      <c r="F106">
-        <v>0.893334646135399</v>
-      </c>
-      <c r="G106">
-        <v>-1.803362060322961</v>
-      </c>
-      <c r="H106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" t="s">
-        <v>79</v>
-      </c>
-      <c r="D107">
-        <v>-1.307456210334532</v>
-      </c>
-      <c r="E107">
-        <v>0.8479178684056462</v>
-      </c>
-      <c r="F107">
-        <v>-2.032215927035765</v>
-      </c>
-      <c r="G107">
-        <v>1.9095296107979</v>
-      </c>
-      <c r="H107">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" t="s">
-        <v>82</v>
-      </c>
-      <c r="D108">
-        <v>0.906860115624798</v>
-      </c>
-      <c r="E108">
-        <v>0.8122662418894508</v>
-      </c>
-      <c r="F108">
-        <v>0.4195104607768282</v>
-      </c>
-      <c r="G108">
-        <v>-0.2063313495368382</v>
-      </c>
-      <c r="H108">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" t="s">
-        <v>81</v>
-      </c>
-      <c r="D109">
-        <v>0.706554270652709</v>
-      </c>
-      <c r="E109">
-        <v>-0.02574528555156137</v>
-      </c>
-      <c r="F109">
-        <v>0.09989286381015486</v>
-      </c>
-      <c r="G109">
-        <v>0.8184767454407612</v>
-      </c>
-      <c r="H109">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" t="s">
-        <v>81</v>
-      </c>
-      <c r="D110">
-        <v>0.6007580397260518</v>
-      </c>
-      <c r="E110">
-        <v>-0.6501984972011415</v>
-      </c>
-      <c r="F110">
-        <v>-0.2287358778058282</v>
-      </c>
-      <c r="G110">
-        <v>0.7194136361301139</v>
-      </c>
-      <c r="H110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111" t="s">
-        <v>79</v>
-      </c>
-      <c r="D111">
-        <v>-1.092821380560519</v>
-      </c>
-      <c r="E111">
-        <v>0.7275100764215968</v>
-      </c>
-      <c r="F111">
-        <v>0.3146658554468746</v>
-      </c>
-      <c r="G111">
-        <v>-0.1896803163935274</v>
-      </c>
-      <c r="H111">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" t="s">
-        <v>81</v>
-      </c>
-      <c r="D112">
-        <v>-0.7786925492884723</v>
-      </c>
-      <c r="E112">
-        <v>-0.8442658739570266</v>
-      </c>
-      <c r="F112">
-        <v>0.2515257194945251</v>
-      </c>
-      <c r="G112">
-        <v>0.6040350547969764</v>
-      </c>
-      <c r="H112">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113" t="s">
-        <v>10</v>
-      </c>
-      <c r="C113" t="s">
-        <v>81</v>
-      </c>
-      <c r="D113">
-        <v>0.008791029014420129</v>
-      </c>
-      <c r="E113">
-        <v>0.1650669415717291</v>
-      </c>
-      <c r="F113">
-        <v>0.2314944124786899</v>
-      </c>
-      <c r="G113">
-        <v>0.3742143590811108</v>
-      </c>
-      <c r="H113">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114" t="s">
-        <v>12</v>
-      </c>
-      <c r="C114" t="s">
-        <v>80</v>
-      </c>
-      <c r="D114">
-        <v>0.4274454383844277</v>
-      </c>
-      <c r="E114">
-        <v>-0.9181037153098365</v>
-      </c>
-      <c r="F114">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G114">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H114">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115" t="s">
-        <v>12</v>
-      </c>
-      <c r="C115" t="s">
-        <v>81</v>
-      </c>
-      <c r="D115">
-        <v>-2.052740539446993</v>
-      </c>
-      <c r="E115">
-        <v>-1.007416905660108</v>
-      </c>
-      <c r="F115">
-        <v>0.288416999272182</v>
-      </c>
-      <c r="G115">
-        <v>-0.6627759831831712</v>
-      </c>
-      <c r="H115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" t="s">
-        <v>12</v>
-      </c>
-      <c r="C116" t="s">
-        <v>81</v>
-      </c>
-      <c r="D116">
-        <v>-1.782913960586113</v>
-      </c>
-      <c r="E116">
-        <v>-0.6299756212144176</v>
-      </c>
-      <c r="F116">
-        <v>0.5205990312330752</v>
-      </c>
-      <c r="G116">
-        <v>-0.3492924766326946</v>
-      </c>
-      <c r="H116">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117" t="s">
-        <v>12</v>
-      </c>
-      <c r="C117" t="s">
-        <v>83</v>
-      </c>
-      <c r="D117">
-        <v>-0.259535019936775</v>
-      </c>
-      <c r="E117">
-        <v>-1.51357631102155</v>
-      </c>
-      <c r="F117">
-        <v>0.28133103499566</v>
-      </c>
-      <c r="G117">
-        <v>-0.2783714632167648</v>
-      </c>
-      <c r="H117">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6751,6 +5643,2938 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H117"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3">
+        <v>-0.5574747128376729</v>
+      </c>
+      <c r="E3">
+        <v>0.09079128689885294</v>
+      </c>
+      <c r="F3">
+        <v>0.3815229241509477</v>
+      </c>
+      <c r="G3">
+        <v>0.1452879090615219</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4">
+        <v>-0.1299976216298829</v>
+      </c>
+      <c r="E4">
+        <v>0.7264908971373215</v>
+      </c>
+      <c r="F4">
+        <v>0.1734068889288403</v>
+      </c>
+      <c r="G4">
+        <v>1.397438665939546</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5">
+        <v>-0.1746485687842852</v>
+      </c>
+      <c r="E5">
+        <v>-0.3440516629722525</v>
+      </c>
+      <c r="F5">
+        <v>0.3246516518557641</v>
+      </c>
+      <c r="G5">
+        <v>-0.1894724763615691</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6">
+        <v>-0.5447978709999376</v>
+      </c>
+      <c r="E6">
+        <v>-0.08939013470924551</v>
+      </c>
+      <c r="F6">
+        <v>0.2022956400079265</v>
+      </c>
+      <c r="G6">
+        <v>1.223239809520513</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8">
+        <v>-1.023645559773101</v>
+      </c>
+      <c r="E8">
+        <v>-0.1950571185501851</v>
+      </c>
+      <c r="F8">
+        <v>0.2330175199311118</v>
+      </c>
+      <c r="G8">
+        <v>-0.3673743700879396</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9">
+        <v>-0.1838781302108423</v>
+      </c>
+      <c r="E9">
+        <v>-0.1972755834591212</v>
+      </c>
+      <c r="F9">
+        <v>0.06460308398013685</v>
+      </c>
+      <c r="G9">
+        <v>0.9677108219141707</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10">
+        <v>0.3612939728313038</v>
+      </c>
+      <c r="E10">
+        <v>0.02011413855760352</v>
+      </c>
+      <c r="F10">
+        <v>-3.226229149704582</v>
+      </c>
+      <c r="G10">
+        <v>-2.124509303992919</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11">
+        <v>-0.3220542533230158</v>
+      </c>
+      <c r="E11">
+        <v>1.024869188951069</v>
+      </c>
+      <c r="F11">
+        <v>0.7078432807053865</v>
+      </c>
+      <c r="G11">
+        <v>-1.488788651187809</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>0.3439782907502662</v>
+      </c>
+      <c r="E12">
+        <v>-1.422201155199607</v>
+      </c>
+      <c r="F12">
+        <v>-2.596294526831652</v>
+      </c>
+      <c r="G12">
+        <v>-1.386678017632773</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13">
+        <v>0.3900039728561599</v>
+      </c>
+      <c r="E13">
+        <v>-1.009954880633531</v>
+      </c>
+      <c r="F13">
+        <v>0.2515257194945251</v>
+      </c>
+      <c r="G13">
+        <v>0.6040350547969764</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14">
+        <v>0.09231223844119693</v>
+      </c>
+      <c r="E14">
+        <v>-1.913126750855901</v>
+      </c>
+      <c r="F14">
+        <v>0.4195104607768282</v>
+      </c>
+      <c r="G14">
+        <v>-0.2063313495368382</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15">
+        <v>1.430304746738134</v>
+      </c>
+      <c r="E15">
+        <v>0.2067577064421887</v>
+      </c>
+      <c r="F15">
+        <v>0.2420360606761059</v>
+      </c>
+      <c r="G15">
+        <v>0.04669778550219194</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16">
+        <v>1.01136348502193</v>
+      </c>
+      <c r="E16">
+        <v>-0.1748919691176447</v>
+      </c>
+      <c r="F16">
+        <v>-0.6760137149362867</v>
+      </c>
+      <c r="G16">
+        <v>1.47454894126003</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17">
+        <v>-0.4998374252596787</v>
+      </c>
+      <c r="E17">
+        <v>0.7196278458589965</v>
+      </c>
+      <c r="F17">
+        <v>0.7350192701430732</v>
+      </c>
+      <c r="G17">
+        <v>-1.133811021071607</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18">
+        <v>0.2607913482830148</v>
+      </c>
+      <c r="E18">
+        <v>0.7955004005631312</v>
+      </c>
+      <c r="F18">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G18">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19">
+        <v>1.350831670822532</v>
+      </c>
+      <c r="E19">
+        <v>-0.3014474608851019</v>
+      </c>
+      <c r="F19">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G19">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20">
+        <v>1.462652674166755</v>
+      </c>
+      <c r="E20">
+        <v>0.1292062937654839</v>
+      </c>
+      <c r="F20">
+        <v>1.182669041479662</v>
+      </c>
+      <c r="G20">
+        <v>-2.610202932287678</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21">
+        <v>-0.3498664855860121</v>
+      </c>
+      <c r="E21">
+        <v>-1.014723692154709</v>
+      </c>
+      <c r="F21">
+        <v>0.2873694988064842</v>
+      </c>
+      <c r="G21">
+        <v>0.3425808901444636</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22">
+        <v>-1.223955685244825</v>
+      </c>
+      <c r="E22">
+        <v>1.281142753952548</v>
+      </c>
+      <c r="F22">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G22">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23">
+        <v>0.5179070850451212</v>
+      </c>
+      <c r="E23">
+        <v>0.4675305835806728</v>
+      </c>
+      <c r="F23">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G23">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24">
+        <v>-0.05756116889432042</v>
+      </c>
+      <c r="E24">
+        <v>0.7586025642385782</v>
+      </c>
+      <c r="F24">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G24">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25">
+        <v>-0.7554598042702086</v>
+      </c>
+      <c r="E25">
+        <v>0.6567310996811981</v>
+      </c>
+      <c r="F25">
+        <v>0.1101881279311937</v>
+      </c>
+      <c r="G25">
+        <v>0.5457677115961386</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27">
+        <v>1.171836154418401</v>
+      </c>
+      <c r="E27">
+        <v>0.06521795499388564</v>
+      </c>
+      <c r="F27">
+        <v>0.5205990312330752</v>
+      </c>
+      <c r="G27">
+        <v>-0.3492924766326946</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28">
+        <v>0.2448824796140681</v>
+      </c>
+      <c r="E28">
+        <v>-0.8168223413693565</v>
+      </c>
+      <c r="F28">
+        <v>-0.1298588224398975</v>
+      </c>
+      <c r="G28">
+        <v>1.826322047227112</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29">
+        <v>1.120174839935586</v>
+      </c>
+      <c r="E29">
+        <v>-0.1126378239392984</v>
+      </c>
+      <c r="F29">
+        <v>0.2314944124786899</v>
+      </c>
+      <c r="G29">
+        <v>0.3742143590811108</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30">
+        <v>-0.2195817119969808</v>
+      </c>
+      <c r="E30">
+        <v>0.4601841119489008</v>
+      </c>
+      <c r="F30">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G30">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31">
+        <v>-0.004578590777285951</v>
+      </c>
+      <c r="E31">
+        <v>0.1051330970640331</v>
+      </c>
+      <c r="F31">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G31">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32">
+        <v>-1.569471018290258</v>
+      </c>
+      <c r="E32">
+        <v>1.540057074870689</v>
+      </c>
+      <c r="F32">
+        <v>0.3146658554468746</v>
+      </c>
+      <c r="G32">
+        <v>-0.1896803163935274</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33">
+        <v>-1.205124956539953</v>
+      </c>
+      <c r="E33">
+        <v>-0.2904509429746304</v>
+      </c>
+      <c r="F33">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G33">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34">
+        <v>-0.4511592700069666</v>
+      </c>
+      <c r="E34">
+        <v>-0.3093638801196507</v>
+      </c>
+      <c r="F34">
+        <v>0.893334646135399</v>
+      </c>
+      <c r="G34">
+        <v>-1.803362060322961</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35">
+        <v>-0.02577116481204763</v>
+      </c>
+      <c r="E35">
+        <v>1.048520780226261</v>
+      </c>
+      <c r="F35">
+        <v>0.3246516518557637</v>
+      </c>
+      <c r="G35">
+        <v>-0.1894724763615693</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36">
+        <v>-0.6405745998250554</v>
+      </c>
+      <c r="E36">
+        <v>0.7550907396172402</v>
+      </c>
+      <c r="F36">
+        <v>-0.8784616779254647</v>
+      </c>
+      <c r="G36">
+        <v>0.5051028971099536</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37">
+        <v>0.8012323856566461</v>
+      </c>
+      <c r="E37">
+        <v>-0.402581899533012</v>
+      </c>
+      <c r="F37">
+        <v>-0.3184432829144211</v>
+      </c>
+      <c r="G37">
+        <v>1.001269756916364</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38">
+        <v>0.9492282876055838</v>
+      </c>
+      <c r="E38">
+        <v>-1.304449593025374</v>
+      </c>
+      <c r="F38">
+        <v>0.2420360606761059</v>
+      </c>
+      <c r="G38">
+        <v>0.04669778550219194</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39">
+        <v>0.6146641253020901</v>
+      </c>
+      <c r="E39">
+        <v>-0.5102473739885162</v>
+      </c>
+      <c r="F39">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G39">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40">
+        <v>-0.2850894140433184</v>
+      </c>
+      <c r="E40">
+        <v>1.308057906297319</v>
+      </c>
+      <c r="F40">
+        <v>0.6182892529975285</v>
+      </c>
+      <c r="G40">
+        <v>-1.016062501613756</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41">
+        <v>-0.6031875208407139</v>
+      </c>
+      <c r="E41">
+        <v>0.1333127524718746</v>
+      </c>
+      <c r="F41">
+        <v>0.6730575767583297</v>
+      </c>
+      <c r="G41">
+        <v>-0.9566833246737863</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42">
+        <v>1.232677313740137</v>
+      </c>
+      <c r="E42">
+        <v>0.2321503562222653</v>
+      </c>
+      <c r="F42">
+        <v>0.2873694988064842</v>
+      </c>
+      <c r="G42">
+        <v>0.3425808901444636</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43">
+        <v>0.1222786302860112</v>
+      </c>
+      <c r="E43">
+        <v>-0.3606368993068123</v>
+      </c>
+      <c r="F43">
+        <v>0.1734068889288418</v>
+      </c>
+      <c r="G43">
+        <v>1.397438665939542</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44">
+        <v>0.5037142975423412</v>
+      </c>
+      <c r="E44">
+        <v>-0.02977427884725369</v>
+      </c>
+      <c r="F44">
+        <v>0.5727042090464712</v>
+      </c>
+      <c r="G44">
+        <v>-0.5941193912957242</v>
+      </c>
+      <c r="H44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45">
+        <v>0.4946477615178588</v>
+      </c>
+      <c r="E45">
+        <v>0.4572055468364684</v>
+      </c>
+      <c r="F45">
+        <v>0.09989286381015486</v>
+      </c>
+      <c r="G45">
+        <v>0.8184767454407612</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46">
+        <v>0.06106940471735506</v>
+      </c>
+      <c r="E46">
+        <v>0.08411433707751106</v>
+      </c>
+      <c r="F46">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G46">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47">
+        <v>-0.5080868026264761</v>
+      </c>
+      <c r="E47">
+        <v>0.9658882465728784</v>
+      </c>
+      <c r="F47">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G47">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49">
+        <v>0.1725873022974022</v>
+      </c>
+      <c r="E49">
+        <v>0.354621530543582</v>
+      </c>
+      <c r="F49">
+        <v>1.140393990225938</v>
+      </c>
+      <c r="G49">
+        <v>-2.078253485797624</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50">
+        <v>-0.301842907985355</v>
+      </c>
+      <c r="E50">
+        <v>-0.2941489461860824</v>
+      </c>
+      <c r="F50">
+        <v>0.288416999272182</v>
+      </c>
+      <c r="G50">
+        <v>-0.6627759831831712</v>
+      </c>
+      <c r="H50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52">
+        <v>-1.752667119028769</v>
+      </c>
+      <c r="E52">
+        <v>-0.6268197064374335</v>
+      </c>
+      <c r="F52">
+        <v>0.7350192701430732</v>
+      </c>
+      <c r="G52">
+        <v>-1.133811021071607</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53">
+        <v>0.2467393006635782</v>
+      </c>
+      <c r="E53">
+        <v>-0.07526538499694292</v>
+      </c>
+      <c r="F53">
+        <v>0.7078432807053868</v>
+      </c>
+      <c r="G53">
+        <v>-1.488788651187809</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54">
+        <v>0.8177951052340048</v>
+      </c>
+      <c r="E54">
+        <v>0.4464834087844466</v>
+      </c>
+      <c r="F54">
+        <v>0.06460308398013674</v>
+      </c>
+      <c r="G54">
+        <v>0.9677108219141703</v>
+      </c>
+      <c r="H54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55">
+        <v>0.8382182385803767</v>
+      </c>
+      <c r="E55">
+        <v>-0.0272424016828803</v>
+      </c>
+      <c r="F55">
+        <v>0.3246516518557637</v>
+      </c>
+      <c r="G55">
+        <v>-0.1894724763615693</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56">
+        <v>0.5234551665087729</v>
+      </c>
+      <c r="E56">
+        <v>0.5972957091695618</v>
+      </c>
+      <c r="F56">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G56">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57">
+        <v>-2.049102833279507</v>
+      </c>
+      <c r="E57">
+        <v>1.52245707306025</v>
+      </c>
+      <c r="F57">
+        <v>0.3146658554468746</v>
+      </c>
+      <c r="G57">
+        <v>-0.1896803163935274</v>
+      </c>
+      <c r="H57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58">
+        <v>1.314765285259702</v>
+      </c>
+      <c r="E58">
+        <v>-0.9698150231558224</v>
+      </c>
+      <c r="F58">
+        <v>-0.2660049921224907</v>
+      </c>
+      <c r="G58">
+        <v>0.3958216343954712</v>
+      </c>
+      <c r="H58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59">
+        <v>-1.771108985484543</v>
+      </c>
+      <c r="E59">
+        <v>0.1106798403409976</v>
+      </c>
+      <c r="F59">
+        <v>0.0001184990954326288</v>
+      </c>
+      <c r="G59">
+        <v>1.509162063712226</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60">
+        <v>-1.429778194779803</v>
+      </c>
+      <c r="E60">
+        <v>1.02673133312414</v>
+      </c>
+      <c r="F60">
+        <v>0.3146658554468746</v>
+      </c>
+      <c r="G60">
+        <v>-0.1896803163935274</v>
+      </c>
+      <c r="H60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62">
+        <v>-0.307163068269531</v>
+      </c>
+      <c r="E62">
+        <v>-0.723313493836271</v>
+      </c>
+      <c r="F62">
+        <v>0.5727042090464712</v>
+      </c>
+      <c r="G62">
+        <v>-0.5941193912957242</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63">
+        <v>-0.968774017440613</v>
+      </c>
+      <c r="E63">
+        <v>0.2490921774505762</v>
+      </c>
+      <c r="F63">
+        <v>0.7078432807053868</v>
+      </c>
+      <c r="G63">
+        <v>-1.488788651187809</v>
+      </c>
+      <c r="H63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64">
+        <v>-0.3180865021614261</v>
+      </c>
+      <c r="E64">
+        <v>-0.2157917893235479</v>
+      </c>
+      <c r="F64">
+        <v>-0.2287358778058282</v>
+      </c>
+      <c r="G64">
+        <v>0.7194136361301139</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65">
+        <v>-0.5703905010013278</v>
+      </c>
+      <c r="E65">
+        <v>0.4267255524380323</v>
+      </c>
+      <c r="F65">
+        <v>1.182669041479662</v>
+      </c>
+      <c r="G65">
+        <v>-2.610202932287678</v>
+      </c>
+      <c r="H65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66">
+        <v>-0.6298514028553761</v>
+      </c>
+      <c r="E66">
+        <v>1.092133285726496</v>
+      </c>
+      <c r="F66">
+        <v>-0.5422870210645181</v>
+      </c>
+      <c r="G66">
+        <v>1.388876534891805</v>
+      </c>
+      <c r="H66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67">
+        <v>-0.8061723903483715</v>
+      </c>
+      <c r="E67">
+        <v>1.04653588195966</v>
+      </c>
+      <c r="F67">
+        <v>-9.128984631952006</v>
+      </c>
+      <c r="G67">
+        <v>-1.960440124448817</v>
+      </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68">
+        <v>-0.3616712956849437</v>
+      </c>
+      <c r="E68">
+        <v>-1.174178520217661</v>
+      </c>
+      <c r="F68">
+        <v>-3.253405139142266</v>
+      </c>
+      <c r="G68">
+        <v>-2.47948693410912</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69">
+        <v>0.07444513953919622</v>
+      </c>
+      <c r="E69">
+        <v>-1.152308147923284</v>
+      </c>
+      <c r="F69">
+        <v>0.06460308398013674</v>
+      </c>
+      <c r="G69">
+        <v>0.9677108219141703</v>
+      </c>
+      <c r="H69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70">
+        <v>1.155873010870637</v>
+      </c>
+      <c r="E70">
+        <v>0.02827412603082538</v>
+      </c>
+      <c r="F70">
+        <v>0.2873694988064842</v>
+      </c>
+      <c r="G70">
+        <v>0.3425808901444636</v>
+      </c>
+      <c r="H70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71">
+        <v>-0.8869893850340613</v>
+      </c>
+      <c r="E71">
+        <v>1.094208413729989</v>
+      </c>
+      <c r="F71">
+        <v>0.8107190549557417</v>
+      </c>
+      <c r="G71">
+        <v>-1.5671917984592</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73">
+        <v>0.172246362207593</v>
+      </c>
+      <c r="E73">
+        <v>0.422777888772521</v>
+      </c>
+      <c r="F73">
+        <v>-0.9132473818725217</v>
+      </c>
+      <c r="G73">
+        <v>1.037208223623976</v>
+      </c>
+      <c r="H73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74">
+        <v>1.146665694860658</v>
+      </c>
+      <c r="E74">
+        <v>0.5009448945229221</v>
+      </c>
+      <c r="F74">
+        <v>0.2314944124786899</v>
+      </c>
+      <c r="G74">
+        <v>0.3742143590811108</v>
+      </c>
+      <c r="H74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75">
+        <v>-0.1168279932989959</v>
+      </c>
+      <c r="E75">
+        <v>-1.206110989211106</v>
+      </c>
+      <c r="F75">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G75">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>80</v>
+      </c>
+      <c r="D76">
+        <v>0.7189813887350064</v>
+      </c>
+      <c r="E76">
+        <v>0.4591797336744849</v>
+      </c>
+      <c r="F76">
+        <v>0.2022956400079261</v>
+      </c>
+      <c r="G76">
+        <v>1.223239809520513</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77">
+        <v>1.475659961011979</v>
+      </c>
+      <c r="E77">
+        <v>0.572556373306108</v>
+      </c>
+      <c r="F77">
+        <v>0.2600731421660941</v>
+      </c>
+      <c r="G77">
+        <v>0.8748420966824551</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78">
+        <v>-0.9058809822050538</v>
+      </c>
+      <c r="E78">
+        <v>-0.4034883207264326</v>
+      </c>
+      <c r="F78">
+        <v>0.08634387553028583</v>
+      </c>
+      <c r="G78">
+        <v>1.251692926007131</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79">
+        <v>0.767677142881948</v>
+      </c>
+      <c r="E79">
+        <v>0.6165935536653225</v>
+      </c>
+      <c r="F79">
+        <v>-0.6380261783104061</v>
+      </c>
+      <c r="G79">
+        <v>1.12292968266167</v>
+      </c>
+      <c r="H79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" t="s">
+        <v>80</v>
+      </c>
+      <c r="D80">
+        <v>0.2319023658857199</v>
+      </c>
+      <c r="E80">
+        <v>0.6175353957100703</v>
+      </c>
+      <c r="F80">
+        <v>0.3296445500602083</v>
+      </c>
+      <c r="G80">
+        <v>-0.1893685563455903</v>
+      </c>
+      <c r="H80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D81">
+        <v>-1.284738051706735</v>
+      </c>
+      <c r="E81">
+        <v>1.141091709364682</v>
+      </c>
+      <c r="F81">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G81">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>81</v>
+      </c>
+      <c r="D82">
+        <v>1.147174436285578</v>
+      </c>
+      <c r="E82">
+        <v>-0.351972635656601</v>
+      </c>
+      <c r="F82">
+        <v>0.2314944124786899</v>
+      </c>
+      <c r="G82">
+        <v>0.3742143590811108</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83">
+        <v>1.271661700671106</v>
+      </c>
+      <c r="E83">
+        <v>-0.6495060670278778</v>
+      </c>
+      <c r="F83">
+        <v>0.2600731421660941</v>
+      </c>
+      <c r="G83">
+        <v>0.8748420966824551</v>
+      </c>
+      <c r="H83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>81</v>
+      </c>
+      <c r="D84">
+        <v>0.5979699843586228</v>
+      </c>
+      <c r="E84">
+        <v>-1.028553418574162</v>
+      </c>
+      <c r="F84">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G84">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>79</v>
+      </c>
+      <c r="D85">
+        <v>0.830906129188078</v>
+      </c>
+      <c r="E85">
+        <v>0.01390939603257811</v>
+      </c>
+      <c r="F85">
+        <v>0.288416999272182</v>
+      </c>
+      <c r="G85">
+        <v>-0.6627759831831712</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" t="s">
+        <v>81</v>
+      </c>
+      <c r="D86">
+        <v>-0.1636441297373128</v>
+      </c>
+      <c r="E86">
+        <v>-1.240846171586163</v>
+      </c>
+      <c r="F86">
+        <v>0.7078432807053868</v>
+      </c>
+      <c r="G86">
+        <v>-1.488788651187809</v>
+      </c>
+      <c r="H86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s">
+        <v>79</v>
+      </c>
+      <c r="D87">
+        <v>0.6945917445816969</v>
+      </c>
+      <c r="E87">
+        <v>-0.04167965907273542</v>
+      </c>
+      <c r="F87">
+        <v>0.6182892529975285</v>
+      </c>
+      <c r="G87">
+        <v>-1.016062501613756</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88">
+        <v>0.2480106836223198</v>
+      </c>
+      <c r="E88">
+        <v>0.6119122906722967</v>
+      </c>
+      <c r="F88">
+        <v>0.288416999272182</v>
+      </c>
+      <c r="G88">
+        <v>-0.6627759831831712</v>
+      </c>
+      <c r="H88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>79</v>
+      </c>
+      <c r="D89">
+        <v>0.08064811654860106</v>
+      </c>
+      <c r="E89">
+        <v>-1.509654325175251</v>
+      </c>
+      <c r="F89">
+        <v>0.2314944124786899</v>
+      </c>
+      <c r="G89">
+        <v>0.3742143590811108</v>
+      </c>
+      <c r="H89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>80</v>
+      </c>
+      <c r="D90">
+        <v>-0.9780118071351053</v>
+      </c>
+      <c r="E90">
+        <v>1.566639690605868</v>
+      </c>
+      <c r="F90">
+        <v>0.3569409067005985</v>
+      </c>
+      <c r="G90">
+        <v>-0.7216297628835812</v>
+      </c>
+      <c r="H90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
+        <v>80</v>
+      </c>
+      <c r="D91">
+        <v>-0.4869225498056208</v>
+      </c>
+      <c r="E91">
+        <v>-0.8175848812058564</v>
+      </c>
+      <c r="F91">
+        <v>0.1660609874243442</v>
+      </c>
+      <c r="G91">
+        <v>0.7499363026989111</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93">
+        <v>0.4712359933849529</v>
+      </c>
+      <c r="E93">
+        <v>0.6546825283354375</v>
+      </c>
+      <c r="F93">
+        <v>-2.221321819121608</v>
+      </c>
+      <c r="G93">
+        <v>-0.8667968714843786</v>
+      </c>
+      <c r="H93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" t="s">
+        <v>80</v>
+      </c>
+      <c r="D94">
+        <v>0.3506192928368125</v>
+      </c>
+      <c r="E94">
+        <v>-1.144042907052204</v>
+      </c>
+      <c r="F94">
+        <v>-0.8693188579642599</v>
+      </c>
+      <c r="G94">
+        <v>2.304156675479724</v>
+      </c>
+      <c r="H94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95">
+        <v>0.903850812208177</v>
+      </c>
+      <c r="E95">
+        <v>0.5256465210136831</v>
+      </c>
+      <c r="F95">
+        <v>0.8469537075393234</v>
+      </c>
+      <c r="G95">
+        <v>-1.093888291637598</v>
+      </c>
+      <c r="H95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" t="s">
+        <v>81</v>
+      </c>
+      <c r="D96">
+        <v>-0.005786376953572689</v>
+      </c>
+      <c r="E96">
+        <v>-0.6624863551260076</v>
+      </c>
+      <c r="F96">
+        <v>-0.650754713907153</v>
+      </c>
+      <c r="G96">
+        <v>0.5790507370244538</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" t="s">
+        <v>80</v>
+      </c>
+      <c r="D97">
+        <v>0.1587354548844314</v>
+      </c>
+      <c r="E97">
+        <v>-0.2108396901132833</v>
+      </c>
+      <c r="F97">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G97">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" t="s">
+        <v>79</v>
+      </c>
+      <c r="D98">
+        <v>-2.33309328961444</v>
+      </c>
+      <c r="E98">
+        <v>-0.4961044670082163</v>
+      </c>
+      <c r="F98">
+        <v>0.3992159579543226</v>
+      </c>
+      <c r="G98">
+        <v>-1.253579209373635</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" t="s">
+        <v>81</v>
+      </c>
+      <c r="D99">
+        <v>0.7940544713507275</v>
+      </c>
+      <c r="E99">
+        <v>0.4395585311086999</v>
+      </c>
+      <c r="F99">
+        <v>0.04291155887133363</v>
+      </c>
+      <c r="G99">
+        <v>1.345905633338301</v>
+      </c>
+      <c r="H99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" t="s">
+        <v>79</v>
+      </c>
+      <c r="D100">
+        <v>0.3721578850811352</v>
+      </c>
+      <c r="E100">
+        <v>0.5036927724238125</v>
+      </c>
+      <c r="F100">
+        <v>0.1101881279311937</v>
+      </c>
+      <c r="G100">
+        <v>0.5457677115961386</v>
+      </c>
+      <c r="H100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>79</v>
+      </c>
+      <c r="D101">
+        <v>-0.4245868376755131</v>
+      </c>
+      <c r="E101">
+        <v>0.3420936808625378</v>
+      </c>
+      <c r="F101">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G101">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H101">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>80</v>
+      </c>
+      <c r="D102">
+        <v>0.4846830297285377</v>
+      </c>
+      <c r="E102">
+        <v>-1.397860970286455</v>
+      </c>
+      <c r="F102">
+        <v>0.6780379652042521</v>
+      </c>
+      <c r="G102">
+        <v>-0.6063821331740676</v>
+      </c>
+      <c r="H102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
+        <v>81</v>
+      </c>
+      <c r="D103">
+        <v>0.2874772580724009</v>
+      </c>
+      <c r="E103">
+        <v>-0.1519867367524503</v>
+      </c>
+      <c r="F103">
+        <v>0.09718142701112946</v>
+      </c>
+      <c r="G103">
+        <v>0.9522327010422177</v>
+      </c>
+      <c r="H103">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" t="s">
+        <v>79</v>
+      </c>
+      <c r="D104">
+        <v>0.8079333191045459</v>
+      </c>
+      <c r="E104">
+        <v>-1.165971131733398</v>
+      </c>
+      <c r="F104">
+        <v>-0.674598966308061</v>
+      </c>
+      <c r="G104">
+        <v>1.284975951435447</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" t="s">
+        <v>81</v>
+      </c>
+      <c r="D105">
+        <v>0.5962863230725786</v>
+      </c>
+      <c r="E105">
+        <v>0.3184150931318233</v>
+      </c>
+      <c r="F105">
+        <v>0.2022956400079261</v>
+      </c>
+      <c r="G105">
+        <v>1.223239809520513</v>
+      </c>
+      <c r="H105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>81</v>
+      </c>
+      <c r="D106">
+        <v>0.519790460000439</v>
+      </c>
+      <c r="E106">
+        <v>0.238412613948167</v>
+      </c>
+      <c r="F106">
+        <v>0.893334646135399</v>
+      </c>
+      <c r="G106">
+        <v>-1.803362060322961</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107">
+        <v>-1.307456210334532</v>
+      </c>
+      <c r="E107">
+        <v>0.8479178684056462</v>
+      </c>
+      <c r="F107">
+        <v>-2.032215927035765</v>
+      </c>
+      <c r="G107">
+        <v>1.9095296107979</v>
+      </c>
+      <c r="H107">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" t="s">
+        <v>82</v>
+      </c>
+      <c r="D108">
+        <v>0.906860115624798</v>
+      </c>
+      <c r="E108">
+        <v>0.8122662418894508</v>
+      </c>
+      <c r="F108">
+        <v>0.4195104607768282</v>
+      </c>
+      <c r="G108">
+        <v>-0.2063313495368382</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" t="s">
+        <v>81</v>
+      </c>
+      <c r="D109">
+        <v>0.706554270652709</v>
+      </c>
+      <c r="E109">
+        <v>-0.02574528555156137</v>
+      </c>
+      <c r="F109">
+        <v>0.09989286381015486</v>
+      </c>
+      <c r="G109">
+        <v>0.8184767454407612</v>
+      </c>
+      <c r="H109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" t="s">
+        <v>81</v>
+      </c>
+      <c r="D110">
+        <v>0.6007580397260518</v>
+      </c>
+      <c r="E110">
+        <v>-0.6501984972011415</v>
+      </c>
+      <c r="F110">
+        <v>-0.2287358778058282</v>
+      </c>
+      <c r="G110">
+        <v>0.7194136361301139</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>79</v>
+      </c>
+      <c r="D111">
+        <v>-1.092821380560519</v>
+      </c>
+      <c r="E111">
+        <v>0.7275100764215968</v>
+      </c>
+      <c r="F111">
+        <v>0.3146658554468746</v>
+      </c>
+      <c r="G111">
+        <v>-0.1896803163935274</v>
+      </c>
+      <c r="H111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>81</v>
+      </c>
+      <c r="D112">
+        <v>-0.7786925492884723</v>
+      </c>
+      <c r="E112">
+        <v>-0.8442658739570266</v>
+      </c>
+      <c r="F112">
+        <v>0.2515257194945251</v>
+      </c>
+      <c r="G112">
+        <v>0.6040350547969764</v>
+      </c>
+      <c r="H112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" t="s">
+        <v>81</v>
+      </c>
+      <c r="D113">
+        <v>0.008791029014420129</v>
+      </c>
+      <c r="E113">
+        <v>0.1650669415717291</v>
+      </c>
+      <c r="F113">
+        <v>0.2314944124786899</v>
+      </c>
+      <c r="G113">
+        <v>0.3742143590811108</v>
+      </c>
+      <c r="H113">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" t="s">
+        <v>80</v>
+      </c>
+      <c r="D114">
+        <v>0.4274454383844277</v>
+      </c>
+      <c r="E114">
+        <v>-0.9181037153098365</v>
+      </c>
+      <c r="F114">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G114">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" t="s">
+        <v>81</v>
+      </c>
+      <c r="D115">
+        <v>-2.052740539446993</v>
+      </c>
+      <c r="E115">
+        <v>-1.007416905660108</v>
+      </c>
+      <c r="F115">
+        <v>0.288416999272182</v>
+      </c>
+      <c r="G115">
+        <v>-0.6627759831831712</v>
+      </c>
+      <c r="H115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>81</v>
+      </c>
+      <c r="D116">
+        <v>-1.782913960586113</v>
+      </c>
+      <c r="E116">
+        <v>-0.6299756212144176</v>
+      </c>
+      <c r="F116">
+        <v>0.5205990312330752</v>
+      </c>
+      <c r="G116">
+        <v>-0.3492924766326946</v>
+      </c>
+      <c r="H116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" t="s">
+        <v>83</v>
+      </c>
+      <c r="D117">
+        <v>-0.259535019936775</v>
+      </c>
+      <c r="E117">
+        <v>-1.51357631102155</v>
+      </c>
+      <c r="F117">
+        <v>0.28133103499566</v>
+      </c>
+      <c r="G117">
+        <v>-0.2783714632167648</v>
+      </c>
+      <c r="H117">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
